--- a/utils/monday_sprint_sprint_2024-36.xlsx
+++ b/utils/monday_sprint_sprint_2024-36.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="199">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>25874</t>
+    <t>6619654227</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>10/05/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>23/05/2024</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,19 +102,22 @@
     <t>Maio</t>
   </si>
   <si>
-    <t>25863</t>
+    <t>6619674289</t>
   </si>
   <si>
     <t>Relatório de AGF material</t>
   </si>
   <si>
-    <t>25872</t>
+    <t>13/05/2024</t>
+  </si>
+  <si>
+    <t>6619665357</t>
   </si>
   <si>
     <t>Relatório de sics diretas</t>
   </si>
   <si>
-    <t>25111</t>
+    <t>6347934769</t>
   </si>
   <si>
     <t>Pontos Qlik Sense 5S</t>
@@ -129,13 +132,13 @@
     <t>Março</t>
   </si>
   <si>
-    <t>25850</t>
+    <t>6619693663</t>
   </si>
   <si>
     <t>IPI Devolvido</t>
   </si>
   <si>
-    <t>25688</t>
+    <t>6531320023</t>
   </si>
   <si>
     <t>Gerar Delivery Note - Exportação</t>
@@ -144,16 +147,22 @@
     <t>26/04/2024</t>
   </si>
   <si>
+    <t>25/05/2024</t>
+  </si>
+  <si>
     <t>Abril</t>
   </si>
   <si>
-    <t>25844</t>
+    <t>6619708767</t>
   </si>
   <si>
     <t>Peso de Conjunto no CPP</t>
   </si>
   <si>
-    <t>23840</t>
+    <t>14/05/2024</t>
+  </si>
+  <si>
+    <t>6631060082</t>
   </si>
   <si>
     <t>Novo Sistema</t>
@@ -162,16 +171,16 @@
     <t>Atualização - Recibo de Embarque</t>
   </si>
   <si>
-    <t>13/05/2024</t>
-  </si>
-  <si>
-    <t>25812</t>
+    <t>15/05/2024</t>
+  </si>
+  <si>
+    <t>6619740141</t>
   </si>
   <si>
     <t>Relatório consumo de eletrodo</t>
   </si>
   <si>
-    <t>22994</t>
+    <t>6003987247</t>
   </si>
   <si>
     <t>Agendamento de tarefa - IROG</t>
@@ -189,7 +198,7 @@
     <t>Fevereiro</t>
   </si>
   <si>
-    <t>24855</t>
+    <t>6431082326</t>
   </si>
   <si>
     <t>Melhoria do sistema de registro - Não Atendido</t>
@@ -198,7 +207,10 @@
     <t>10/04/2024</t>
   </si>
   <si>
-    <t>24901</t>
+    <t>27/05/2024</t>
+  </si>
+  <si>
+    <t>6480059400</t>
   </si>
   <si>
     <t>Sistema de Previsão de Vendas (Ofertas e Forecast) Part II</t>
@@ -210,25 +222,28 @@
     <t>Semana 3</t>
   </si>
   <si>
-    <t>25805</t>
+    <t>6532941211</t>
   </si>
   <si>
     <t>Relatório de modelo bloqueados - Incluir coluna com código mestre quando conjunto</t>
   </si>
   <si>
-    <t>25742</t>
+    <t>6531021824</t>
   </si>
   <si>
     <t>Sistema de endereçamento Almoxarifado</t>
   </si>
   <si>
-    <t>25746</t>
+    <t>22/05/2024</t>
+  </si>
+  <si>
+    <t>6530900440</t>
   </si>
   <si>
     <t>Sistema almoxarifado - Movimentação</t>
   </si>
   <si>
-    <t>25359</t>
+    <t>6573995461</t>
   </si>
   <si>
     <t>Indefinido</t>
@@ -240,34 +255,46 @@
     <t>03/05/2024</t>
   </si>
   <si>
-    <t>25360</t>
+    <t>26/05/2024</t>
+  </si>
+  <si>
+    <t>6620014363</t>
   </si>
   <si>
     <t>Criar estrutura de setor x operação para REB VI</t>
   </si>
   <si>
-    <t>25862</t>
+    <t>12/05/2024</t>
+  </si>
+  <si>
+    <t>6619683223</t>
   </si>
   <si>
     <t>Bloqueio de NCM</t>
   </si>
   <si>
-    <t>22418</t>
+    <t>6534249669</t>
   </si>
   <si>
     <t>Melhorias Sistema de Apontamentos Moldagem ULE - Tablet para pintura</t>
   </si>
   <si>
-    <t>25989</t>
+    <t>6619123710</t>
   </si>
   <si>
     <t>QSense - Nova aplicação - Movimentação por setor</t>
   </si>
   <si>
+    <t>24/05/2024</t>
+  </si>
+  <si>
+    <t>6620363765</t>
+  </si>
+  <si>
     <t>Controle de tempo previsto x realizado Gestão à vista Rebarbação VI</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>6627171867</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -276,28 +303,34 @@
     <t>AJUSTES CONDIÇÃO DE PAGAMENTO OFERTA / CPC - Painel de gestão à vista status dos eventos (Chamado Matriz)</t>
   </si>
   <si>
+    <t>6631499575</t>
+  </si>
+  <si>
     <t>Tela de acompanhamento de status de eventos</t>
   </si>
   <si>
-    <t>25175</t>
+    <t>6350664258</t>
   </si>
   <si>
     <t>Dados Para Projeto Andon - Komatsu - Tabelas de Apontamento</t>
   </si>
   <si>
+    <t>09/05/2024</t>
+  </si>
+  <si>
+    <t>6699956491</t>
+  </si>
+  <si>
     <t>Dados Para Projeto Andon - Komatsu - Tabelas de Apontamento (DELTRACTOR)</t>
   </si>
   <si>
-    <t>23/05/2024</t>
-  </si>
-  <si>
-    <t>6090</t>
+    <t>6350727462</t>
   </si>
   <si>
     <t>Sistema Novo de Revisão de Documentos - Sprint FINAL II</t>
   </si>
   <si>
-    <t>21809</t>
+    <t>6269809958</t>
   </si>
   <si>
     <t>Relatório de Faturamento por Sequência</t>
@@ -306,22 +339,19 @@
     <t>15/03/2024</t>
   </si>
   <si>
+    <t>6644598692</t>
+  </si>
+  <si>
     <t>Integração dos dados comerciais Benner e SPS</t>
   </si>
   <si>
-    <t>15/05/2024</t>
-  </si>
-  <si>
-    <t>25487</t>
+    <t>6635721202</t>
   </si>
   <si>
     <t>Sistema de cadastro de modelos - vida útil dos modelos</t>
   </si>
   <si>
-    <t>14/05/2024</t>
-  </si>
-  <si>
-    <t>25570</t>
+    <t>6446243882</t>
   </si>
   <si>
     <t>Migração das tabelas da aplicação de requisição - Qliksense</t>
@@ -330,139 +360,157 @@
     <t>12/04/2024</t>
   </si>
   <si>
-    <t>25551</t>
+    <t>6446301624</t>
   </si>
   <si>
     <t>Melhorias Sistemas de Custeio - Gerar log em TXT rotina de Cálculo</t>
   </si>
   <si>
-    <t>25944</t>
+    <t>6619376717</t>
   </si>
   <si>
     <t>Erro no totalizador de DIFA e BC do PIS e COFINS</t>
   </si>
   <si>
-    <t>25985</t>
+    <t>6619176916</t>
   </si>
   <si>
     <t>Campo para identificar peça ensaiada</t>
   </si>
   <si>
-    <t>25792</t>
+    <t>6619756740</t>
   </si>
   <si>
     <t>Melhorias Sistema de Custeio - Beneficiamento de Terceiros</t>
   </si>
   <si>
-    <t>25984</t>
+    <t>20/05/2024</t>
+  </si>
+  <si>
+    <t>6619189018</t>
   </si>
   <si>
     <t>Estorno romaneio conjunto</t>
   </si>
   <si>
-    <t>25966</t>
+    <t>6619342728</t>
   </si>
   <si>
     <t>Melhoria - Importar Tabela</t>
   </si>
   <si>
-    <t>25947</t>
+    <t>6619367755</t>
   </si>
   <si>
     <t>Incluir Coluna Planilha MPS - Data de Linha de Moldagem</t>
   </si>
   <si>
-    <t>25992</t>
+    <t>6620578614</t>
   </si>
   <si>
     <t>Migração de Modelo com estorno do Deposito</t>
   </si>
   <si>
-    <t>25961</t>
+    <t>6619355138</t>
   </si>
   <si>
     <t>Acrescentar coluna com o nome do cliente no relatório em aberto por setor ( sistema PCP / ALT+D))</t>
   </si>
   <si>
-    <t>25886</t>
+    <t>6619627361</t>
   </si>
   <si>
     <t>ATUALIZAÇÕES TELA COPIAR CPP</t>
   </si>
   <si>
-    <t>25828</t>
+    <t>18/05/2024</t>
+  </si>
+  <si>
+    <t>6619719789</t>
   </si>
   <si>
     <t>LIBERAÇÃO DE ACESSO AUTOMÁTICO – POSTO DE CÓPIAS ELETRÔNICO</t>
   </si>
   <si>
-    <t>25995</t>
+    <t>6620590474</t>
   </si>
   <si>
     <t>Sistema de Corridas - Consistência Consumo kWh</t>
   </si>
   <si>
-    <t>25686</t>
+    <t>21/05/2024</t>
+  </si>
+  <si>
+    <t>6631448333</t>
   </si>
   <si>
     <t>Criar estrutura de tabelas</t>
   </si>
   <si>
+    <t>6631449885</t>
+  </si>
+  <si>
     <t>Criar interface Web</t>
   </si>
   <si>
+    <t>6631451688</t>
+  </si>
+  <si>
     <t>Criar as telas de cadastro solicitações</t>
   </si>
   <si>
+    <t>6631452880</t>
+  </si>
+  <si>
     <t>Gerar OC Direta</t>
   </si>
   <si>
+    <t>16/05/2024</t>
+  </si>
+  <si>
+    <t>6631454321</t>
+  </si>
+  <si>
     <t>Controle de itens novos</t>
   </si>
   <si>
-    <t>25474</t>
+    <t>6446515897</t>
   </si>
   <si>
     <t>Pré-embarque</t>
   </si>
   <si>
-    <t>26124</t>
+    <t>6681807667</t>
   </si>
   <si>
     <t>Consulta ordens de compra por projeto</t>
   </si>
   <si>
-    <t>21/05/2024</t>
-  </si>
-  <si>
-    <t>26112</t>
+    <t>6715394260</t>
   </si>
   <si>
     <t>Melhoria Sistema de Custeio - Acabamento</t>
   </si>
   <si>
-    <t>27/05/2024</t>
-  </si>
-  <si>
-    <t>25733</t>
+    <t>6619773687</t>
   </si>
   <si>
     <t>BLOQUEIO PDF – POSTO DE CÓPIAS ELETRÔNICO</t>
   </si>
   <si>
-    <t>25764</t>
+    <t>6619765760</t>
   </si>
   <si>
     <t>Relatórios de Suprimentos</t>
   </si>
   <si>
-    <t>25978</t>
+    <t>6619256893</t>
   </si>
   <si>
     <t>ERRO: Sistema Apontamento Moldagem UPR</t>
   </si>
   <si>
-    <t>25894</t>
+    <t>6619590879</t>
   </si>
   <si>
     <t>Melhorias de Sistemas Corridas - Cálculo Relatório Planilha de Custeio</t>
@@ -474,7 +522,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-36</t>
+    <t>Fev/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -1122,7 +1170,7 @@
         <v>23</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1139,7 +1187,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1151,10 +1199,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -1169,7 +1217,7 @@
         <v>23</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1186,7 +1234,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1198,10 +1246,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1213,7 +1261,7 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>24</v>
@@ -1225,15 +1273,15 @@
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1245,10 +1293,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1280,7 +1328,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1292,10 +1340,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1307,10 +1355,10 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1319,15 +1367,15 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1339,10 +1387,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1357,7 +1405,7 @@
         <v>23</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1374,22 +1422,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1401,10 +1449,10 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1421,7 +1469,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1433,10 +1481,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1451,7 +1499,7 @@
         <v>23</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1468,7 +1516,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1480,13 +1528,13 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>21</v>
@@ -1495,10 +1543,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1507,15 +1555,15 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1527,10 +1575,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1542,10 +1590,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1557,12 +1605,12 @@
         <v>27</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1574,10 +1622,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1589,10 +1637,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1601,15 +1649,15 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1621,10 +1669,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1636,10 +1684,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1648,15 +1696,15 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1668,10 +1716,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1683,10 +1731,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1695,15 +1743,15 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1715,10 +1763,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1730,7 +1778,7 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>24</v>
@@ -1742,30 +1790,30 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1777,10 +1825,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1789,7 +1837,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>28</v>
@@ -1797,7 +1845,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1809,13 +1857,13 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>21</v>
@@ -1827,7 +1875,7 @@
         <v>23</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1844,7 +1892,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1856,10 +1904,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1874,7 +1922,7 @@
         <v>23</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1891,7 +1939,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1903,13 +1951,13 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>21</v>
@@ -1918,10 +1966,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1930,15 +1978,15 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1950,10 +1998,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1968,7 +2016,7 @@
         <v>23</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1985,7 +2033,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1997,10 +2045,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -2015,7 +2063,7 @@
         <v>23</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -2032,25 +2080,25 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>21</v>
@@ -2059,10 +2107,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -2079,22 +2127,22 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2106,10 +2154,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2126,25 +2174,25 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>21</v>
@@ -2153,10 +2201,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2165,46 +2213,46 @@
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K26" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
       </c>
@@ -2212,7 +2260,7 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>28</v>
@@ -2220,22 +2268,22 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2247,10 +2295,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2259,15 +2307,15 @@
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2279,13 +2327,13 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>21</v>
@@ -2294,10 +2342,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2306,15 +2354,15 @@
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2326,10 +2374,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2341,10 +2389,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2353,7 +2401,7 @@
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>28</v>
@@ -2361,7 +2409,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2373,10 +2421,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2388,10 +2436,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2408,7 +2456,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2420,10 +2468,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2435,7 +2483,7 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>24</v>
@@ -2450,12 +2498,12 @@
         <v>27</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2467,10 +2515,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2482,10 +2530,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2497,12 +2545,12 @@
         <v>27</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2514,10 +2562,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2532,7 +2580,7 @@
         <v>23</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2549,7 +2597,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2561,10 +2609,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2579,7 +2627,7 @@
         <v>23</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2596,7 +2644,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2608,10 +2656,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2626,7 +2674,7 @@
         <v>23</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2643,7 +2691,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2655,10 +2703,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2673,7 +2721,7 @@
         <v>23</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2690,7 +2738,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2702,10 +2750,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2720,7 +2768,7 @@
         <v>23</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2737,7 +2785,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2749,10 +2797,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2767,7 +2815,7 @@
         <v>23</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -2784,7 +2832,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2796,10 +2844,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2814,7 +2862,7 @@
         <v>23</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -2831,7 +2879,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2843,10 +2891,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -2861,7 +2909,7 @@
         <v>23</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -2878,7 +2926,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2890,10 +2938,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -2908,7 +2956,7 @@
         <v>23</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>136</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
@@ -2925,7 +2973,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -2937,10 +2985,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -2955,7 +3003,7 @@
         <v>23</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>136</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -2972,7 +3020,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -2984,10 +3032,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -3002,7 +3050,7 @@
         <v>23</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -3019,7 +3067,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -3031,10 +3079,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3046,10 +3094,10 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -3066,7 +3114,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3078,10 +3126,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
@@ -3093,10 +3141,10 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3113,7 +3161,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3125,10 +3173,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3140,10 +3188,10 @@
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3160,7 +3208,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3172,10 +3220,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3187,10 +3235,10 @@
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>25</v>
@@ -3207,7 +3255,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3219,10 +3267,10 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
@@ -3234,10 +3282,10 @@
         <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>136</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>25</v>
@@ -3254,7 +3302,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3266,10 +3314,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3281,10 +3329,10 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>25</v>
@@ -3296,12 +3344,12 @@
         <v>27</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -3313,10 +3361,10 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>20</v>
@@ -3328,10 +3376,10 @@
         <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>25</v>
@@ -3340,7 +3388,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>28</v>
@@ -3348,7 +3396,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3360,10 +3408,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -3375,10 +3423,10 @@
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>142</v>
+        <v>64</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>25</v>
@@ -3387,7 +3435,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>28</v>
@@ -3395,7 +3443,7 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
@@ -3407,10 +3455,10 @@
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
@@ -3425,7 +3473,7 @@
         <v>23</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>136</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>25</v>
@@ -3442,7 +3490,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
@@ -3454,10 +3502,10 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
@@ -3472,7 +3520,7 @@
         <v>23</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>25</v>
@@ -3489,7 +3537,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
@@ -3501,10 +3549,10 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>20</v>
@@ -3519,7 +3567,7 @@
         <v>23</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>25</v>
@@ -3536,7 +3584,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
@@ -3548,10 +3596,10 @@
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>20</v>
@@ -3594,23 +3642,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="B2" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="D2" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="E2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3618,16 +3666,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3638,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>18.67</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -3646,7 +3694,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3659,7 +3707,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -3667,7 +3715,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3698,12 +3746,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="B2">
         <v>54</v>
@@ -3717,7 +3765,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>18.67</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -3727,25 +3775,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3762,13 +3810,13 @@
         <v>47</v>
       </c>
       <c r="G10" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3780,21 +3828,21 @@
         <v>54</v>
       </c>
       <c r="P10" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="E11">
         <v>5</v>
       </c>
       <c r="G11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H11">
         <v>7</v>
@@ -3806,21 +3854,21 @@
         <v>54</v>
       </c>
       <c r="M11" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="Q11">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -3832,59 +3880,53 @@
         <v>47</v>
       </c>
       <c r="J12" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="Q12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
-      <c r="P13" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q13">
-        <v>10</v>
-      </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -3892,7 +3934,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3900,7 +3942,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3908,7 +3950,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3916,10 +3958,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3927,7 +3969,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3935,142 +3977,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>93</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>32</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>33</v>
+        <v>108</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>38</v>
+        <v>126</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>39</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>40</v>
+        <v>128</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>41</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>45</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>46</v>
+        <v>157</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>48</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
